--- a/artfynd/A 27902-2023 artfynd.xlsx
+++ b/artfynd/A 27902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81439967</v>
+        <v>137531228</v>
       </c>
       <c r="B2" t="n">
-        <v>103403</v>
+        <v>105145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223246</v>
+        <v>221178</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Bäckbräsma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Cardamine amara</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Huds.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>400 m SO Fogdarödshemmet, Sk</t>
+          <t>500 m O Dalen, Sk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410959</v>
+        <v>411172</v>
       </c>
       <c r="R2" t="n">
-        <v>6199220</v>
+        <v>6199053</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-07-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-07-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,26 +764,668 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Längs skogsbilväg</t>
+          <t>alsumpskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137531228</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>137532156</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100098</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222306</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stjärnstarr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carex echinata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Murray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>500 m OSO (f.d.) Fogdarödshemmet, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411180</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6199153</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>ung sumpskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532156</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137532522</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100102</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222308</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rankstarr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carex elongata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>500 m OSO (f.d.) Fogdarödshemmet, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411180</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6199153</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>ung sumpskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532522</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137532285</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100205</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>500 m O Dalen, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411172</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6199053</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>alsumpskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532285</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137532673</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98517</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222736</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Majbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Athyrium filix-femina</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>500 m OSO (f.d.) Fogdarödshemmet, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>411180</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6199153</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>ung sumpskog</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137532673</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137530823</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103127</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223037</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Humleblomster</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>500 m OSO (f.d.) Fogdarödshemmet, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>411180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6199153</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>ung sumpskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Torbjörn Tyler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137530823</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>81439967</v>
+      </c>
+      <c r="B8" t="n">
+        <v>103403</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223246</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsalm</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ulmus glabra</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>400 m SO Fogdarödshemmet, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>410959</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6199220</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Höör</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2010-07-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2010-07-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Längs skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Stefan Andersson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Torbjörn Tyler</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Skånes Flora Millora 2008-2015</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/81439967</t>
         </is>
@@ -792,6 +1434,12 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
